--- a/test/integration/01-out.xlsx
+++ b/test/integration/01-out.xlsx
@@ -15,6 +15,212 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="67">
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>coefficient</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Buğday</t>
+  </si>
+  <si>
+    <t>Buğday+SM</t>
+  </si>
+  <si>
+    <t>Buğday satış</t>
+  </si>
+  <si>
+    <t>Silajlık mısır satış</t>
+  </si>
+  <si>
+    <t>Çeltik</t>
+  </si>
+  <si>
+    <t>Çeltik satış</t>
+  </si>
+  <si>
+    <t>Fındık</t>
+  </si>
+  <si>
+    <t>Fındık satış</t>
+  </si>
+  <si>
+    <t>Buğday+lahana</t>
+  </si>
+  <si>
+    <t>Lahana satış</t>
+  </si>
+  <si>
+    <t>Süt sığırcılığı</t>
+  </si>
+  <si>
+    <t>igk6</t>
+  </si>
+  <si>
+    <t>igk7</t>
+  </si>
+  <si>
+    <t>igk8</t>
+  </si>
+  <si>
+    <t>Sermaye temini</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>relation</t>
+  </si>
+  <si>
+    <t>rhs</t>
+  </si>
+  <si>
+    <t>Toplam arazi</t>
+  </si>
+  <si>
+    <t>&lt;=</t>
+  </si>
+  <si>
+    <t>Toplam kuru tarla arazisi</t>
+  </si>
+  <si>
+    <t>Toplam sulu tarla arazisi</t>
+  </si>
+  <si>
+    <t>Meyve arazisi</t>
+  </si>
+  <si>
+    <t>Sebze arazisi</t>
+  </si>
+  <si>
+    <t>Buğday arazisi</t>
+  </si>
+  <si>
+    <t>Silajlık mısır arazisi</t>
+  </si>
+  <si>
+    <t>Çeltik arazisi</t>
+  </si>
+  <si>
+    <t>Fındık arazisi</t>
+  </si>
+  <si>
+    <t>Lahana arazisi</t>
+  </si>
+  <si>
+    <t>Buğday transfer</t>
+  </si>
+  <si>
+    <t>Silajlık mısır transfer</t>
+  </si>
+  <si>
+    <t>Çeltik transfer</t>
+  </si>
+  <si>
+    <t>Lahana transfer</t>
+  </si>
+  <si>
+    <t>Fındık transfer</t>
+  </si>
+  <si>
+    <t>İşgücü Ocak</t>
+  </si>
+  <si>
+    <t>İşgücü Şubat</t>
+  </si>
+  <si>
+    <t>İşgücü Mart</t>
+  </si>
+  <si>
+    <t>İşgücü Nisan</t>
+  </si>
+  <si>
+    <t>İşgücü Mayıs</t>
+  </si>
+  <si>
+    <t>İşgücü Haziran</t>
+  </si>
+  <si>
+    <t>İşgücü Temmuz</t>
+  </si>
+  <si>
+    <t>İşgücü Ağustos</t>
+  </si>
+  <si>
+    <t>İşgücü Eylül</t>
+  </si>
+  <si>
+    <t>İşgücü Ekim</t>
+  </si>
+  <si>
+    <t>İşgücü Kasım</t>
+  </si>
+  <si>
+    <t>İşgücü Aralık</t>
+  </si>
+  <si>
+    <t>Saman</t>
+  </si>
+  <si>
+    <t>İşletme sermayesi</t>
+  </si>
+  <si>
+    <t>Ahır Yeri</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>OPTIMAL</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Solution is optimal</t>
+  </si>
+  <si>
+    <t>reduced_cost</t>
+  </si>
+  <si>
+    <t>original_value</t>
+  </si>
+  <si>
+    <t>lower_bound</t>
+  </si>
+  <si>
+    <t>upper_bound</t>
+  </si>
+  <si>
+    <t>is_basic_variable</t>
+  </si>
+  <si>
+    <t>shadow_price</t>
+  </si>
+  <si>
+    <t>slack_or_surplus</t>
+  </si>
+  <si>
+    <t>neither_bounds_are_binding</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -344,170 +550,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Buğday</t>
-        </is>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
       <c r="B2">
         <v>-239.38</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Buğday+SM</t>
-        </is>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <v>-280.73</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Buğday satış</t>
-        </is>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>5</v>
       </c>
       <c r="B4">
         <v>2.3</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Silajlık mısır satış</t>
-        </is>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
       <c r="B5">
         <v>1.33</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Çeltik</t>
-        </is>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>7</v>
       </c>
       <c r="B6">
         <v>-469.2</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Çeltik satış</t>
-        </is>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
       </c>
       <c r="B7">
         <v>2.5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Fındık</t>
-        </is>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>9</v>
       </c>
       <c r="B8">
         <v>-901.47</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fındık satış</t>
-        </is>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>10</v>
       </c>
       <c r="B9">
         <v>25.25</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Buğday+lahana</t>
-        </is>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>11</v>
       </c>
       <c r="B10">
         <v>-1899.15</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Lahana satış</t>
-        </is>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>12</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Süt sığırcılığı</t>
-        </is>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>13</v>
       </c>
       <c r="B12">
         <v>5806.18</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>igk6</t>
-        </is>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
       </c>
       <c r="B13">
         <v>-12.5</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>igk7</t>
-        </is>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>15</v>
       </c>
       <c r="B14">
         <v>-12.5</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>igk8</t>
-        </is>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>16</v>
       </c>
       <c r="B15">
         <v>-12.5</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sermaye temini</t>
-        </is>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>17</v>
       </c>
       <c r="B16">
         <v>-0.25</v>
@@ -520,152 +699,113 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="3.5703125" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="8" width="6.140625" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" customWidth="1"/>
-    <col min="10" max="10" width="6.140625" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" customWidth="1"/>
-    <col min="15" max="15" width="4.42578125" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="3.5703125" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" customWidth="1"/>
+    <col min="9" max="9" width="6.140625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.28515625" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" customWidth="1"/>
     <col min="16" max="16" width="4.42578125" customWidth="1"/>
     <col min="17" max="17" width="4.42578125" customWidth="1"/>
-    <col min="18" max="18" width="13.28515625" customWidth="1"/>
+    <col min="18" max="18" width="4.42578125" customWidth="1"/>
+    <col min="19" max="19" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>constraint</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>relation</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>rhs</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Buğday</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Buğday+SM</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Buğday satış</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Silajlık mısır satış</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Çeltik</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Çeltik satış</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Fındık</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Fındık satış</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Buğday+lahana</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Lahana satış</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Süt sığırcılığı</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>igk6</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>igk7</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>igk8</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Sermaye temini</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Toplam arazi</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C2">
+    <row r="1" spans="1:19">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2">
         <v>602620</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -694,29 +834,25 @@
       <c r="R2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Toplam kuru tarla arazisi</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C3">
+      <c r="S2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3">
         <v>359641</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -754,38 +890,34 @@
       <c r="R3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Toplam sulu tarla arazisi</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C4">
+      <c r="S3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
+      <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4">
         <v>88270</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
       <c r="E4">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -814,24 +946,20 @@
       <c r="R4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Meyve arazisi</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C5">
+      <c r="S4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5">
         <v>25396</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
         <v>0</v>
       </c>
@@ -848,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -874,24 +1002,20 @@
       <c r="R5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sebze arazisi</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C6">
+      <c r="S5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
         <v>74740</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6">
         <v>0</v>
       </c>
@@ -914,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -934,29 +1058,25 @@
       <c r="R6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Buğday arazisi</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C7">
+      <c r="S6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7">
         <v>253452</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -974,10 +1094,10 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -994,29 +1114,25 @@
       <c r="R7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Silajlık mısır arazisi</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C8">
+      <c r="S7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8">
         <v>57380</v>
       </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1054,24 +1170,20 @@
       <c r="R8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Çeltik arazisi</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C9">
+      <c r="S8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9">
         <v>334876</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
       <c r="E9">
         <v>0</v>
       </c>
@@ -1082,10 +1194,10 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1114,24 +1226,20 @@
       <c r="R9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fındık arazisi</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C10">
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10">
         <v>20531</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
       <c r="E10">
         <v>0</v>
       </c>
@@ -1148,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -1174,24 +1282,20 @@
       <c r="R10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Lahana arazisi</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C11">
+      <c r="S10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11">
         <v>30525</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
       <c r="E11">
         <v>0</v>
       </c>
@@ -1214,10 +1318,10 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1234,32 +1338,28 @@
       <c r="R11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Buğday transfer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>0</v>
+      <c r="S11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
       </c>
       <c r="D12">
-        <v>-437.5</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>-437.5</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>-437.5</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1294,35 +1394,31 @@
       <c r="R12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Silajlık mısır transfer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>0</v>
+      <c r="S12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <v>-827.33</v>
       </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
       <c r="G13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -1340,11 +1436,11 @@
         <v>0</v>
       </c>
       <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
         <v>1400</v>
       </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
       <c r="P13">
         <v>0</v>
       </c>
@@ -1354,20 +1450,16 @@
       <c r="R13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Çeltik transfer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>0</v>
+      <c r="S13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -1382,13 +1474,13 @@
         <v>0</v>
       </c>
       <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>-700</v>
       </c>
-      <c r="I14">
-        <v>1</v>
-      </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1414,20 +1506,16 @@
       <c r="R14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Lahana transfer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>0</v>
+      <c r="S14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -1454,13 +1542,13 @@
         <v>0</v>
       </c>
       <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
         <v>-6000</v>
       </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
       <c r="N15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -1474,20 +1562,16 @@
       <c r="R15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fındık transfer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>0</v>
+      <c r="S15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -1508,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
         <v>-93.75</v>
       </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -1534,24 +1618,20 @@
       <c r="R16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>İşgücü Ocak</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C17">
+      <c r="S16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17">
         <v>11528550</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
       <c r="E17">
         <v>0</v>
       </c>
@@ -1580,11 +1660,11 @@
         <v>0</v>
       </c>
       <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
         <v>27.42</v>
       </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
       <c r="P17">
         <v>0</v>
       </c>
@@ -1594,24 +1674,20 @@
       <c r="R17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>İşgücü Şubat</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C18">
+      <c r="S17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
+      <c r="A18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18">
         <v>11528550</v>
       </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
       <c r="E18">
         <v>0</v>
       </c>
@@ -1640,11 +1716,11 @@
         <v>0</v>
       </c>
       <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
         <v>25.55</v>
       </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
       <c r="P18">
         <v>0</v>
       </c>
@@ -1654,24 +1730,20 @@
       <c r="R18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>İşgücü Mart</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C19">
+      <c r="S18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19">
         <v>11528550</v>
       </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
       <c r="E19">
         <v>0</v>
       </c>
@@ -1700,11 +1772,11 @@
         <v>0</v>
       </c>
       <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
         <v>27.42</v>
       </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
       <c r="P19">
         <v>0</v>
       </c>
@@ -1714,57 +1786,53 @@
       <c r="R19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>İşgücü Nisan</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C20">
+      <c r="S19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20">
         <v>11528550</v>
-      </c>
-      <c r="D20">
-        <v>0.88</v>
       </c>
       <c r="E20">
         <v>0.88</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <v>1.76</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
       <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
         <v>2.5</v>
       </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
       <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
         <v>1.76</v>
       </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
       <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
         <v>27.32</v>
       </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
       <c r="P20">
         <v>0</v>
       </c>
@@ -1774,24 +1842,20 @@
       <c r="R20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>İşgücü Mayıs</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C21">
+      <c r="S20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21">
         <v>11528550</v>
       </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
       <c r="E21">
         <v>0</v>
       </c>
@@ -1802,11 +1866,11 @@
         <v>0</v>
       </c>
       <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
         <v>0.88</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
       <c r="J21">
         <v>0</v>
       </c>
@@ -1820,11 +1884,11 @@
         <v>0</v>
       </c>
       <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
         <v>27.42</v>
       </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
       <c r="P21">
         <v>0</v>
       </c>
@@ -1834,24 +1898,20 @@
       <c r="R21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>İşgücü Haziran</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C22">
+      <c r="S21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22">
         <v>11528550</v>
       </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
       <c r="E22">
         <v>0</v>
       </c>
@@ -1862,11 +1922,11 @@
         <v>0</v>
       </c>
       <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
         <v>1.08</v>
       </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
       <c r="J22">
         <v>0</v>
       </c>
@@ -1880,98 +1940,90 @@
         <v>0</v>
       </c>
       <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
         <v>27.37</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>-1</v>
       </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
       <c r="Q22">
         <v>0</v>
       </c>
       <c r="R22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>İşgücü Temmuz</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C23">
+      <c r="S22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23">
         <v>11528550</v>
-      </c>
-      <c r="D23">
-        <v>3.17</v>
       </c>
       <c r="E23">
         <v>3.17</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
         <v>5.2</v>
       </c>
-      <c r="I23">
-        <v>0</v>
-      </c>
       <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
         <v>8.5</v>
       </c>
-      <c r="K23">
-        <v>0</v>
-      </c>
       <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>6.34</v>
       </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
       <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
         <v>27.42</v>
       </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
       <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
         <v>-1</v>
       </c>
-      <c r="Q23">
-        <v>0</v>
-      </c>
       <c r="R23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>İşgücü Ağustos</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C24">
+      <c r="S23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
+      <c r="A24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24">
         <v>11528550</v>
       </c>
-      <c r="D24">
-        <v>0</v>
-      </c>
       <c r="E24">
         <v>0</v>
       </c>
@@ -1988,11 +2040,11 @@
         <v>0</v>
       </c>
       <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
         <v>12.5</v>
       </c>
-      <c r="K24">
-        <v>0</v>
-      </c>
       <c r="L24">
         <v>0</v>
       </c>
@@ -2000,71 +2052,67 @@
         <v>0</v>
       </c>
       <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
         <v>27.42</v>
       </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
       <c r="P24">
         <v>0</v>
       </c>
       <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
         <v>-1</v>
       </c>
-      <c r="R24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>İşgücü Eylül</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C25">
+      <c r="S24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25">
         <v>11528550</v>
-      </c>
-      <c r="D25">
-        <v>0.73</v>
       </c>
       <c r="E25">
         <v>0.73</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
         <v>10.25</v>
       </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
       <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
         <v>2.5</v>
       </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
       <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>1.46</v>
       </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
       <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25">
         <v>27.37</v>
       </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
       <c r="P25">
         <v>0</v>
       </c>
@@ -2074,39 +2122,35 @@
       <c r="R25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>İşgücü Ekim</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C26">
+      <c r="S25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
+      <c r="A26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26">
         <v>11528550</v>
-      </c>
-      <c r="D26">
-        <v>0.88</v>
       </c>
       <c r="E26">
         <v>0.88</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
         <v>2.3</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
       <c r="J26">
         <v>0</v>
       </c>
@@ -2114,17 +2158,17 @@
         <v>0</v>
       </c>
       <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>1.76</v>
       </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
       <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26">
         <v>27.42</v>
       </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
       <c r="P26">
         <v>0</v>
       </c>
@@ -2134,24 +2178,20 @@
       <c r="R26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>İşgücü Kasım</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C27">
+      <c r="S26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19">
+      <c r="A27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27">
         <v>11528550</v>
       </c>
-      <c r="D27">
-        <v>0</v>
-      </c>
       <c r="E27">
         <v>0</v>
       </c>
@@ -2180,11 +2220,11 @@
         <v>0</v>
       </c>
       <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
         <v>27.32</v>
       </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
       <c r="P27">
         <v>0</v>
       </c>
@@ -2194,24 +2234,20 @@
       <c r="R27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>İşgücü Aralık</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C28">
+      <c r="S27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
+      <c r="A28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28">
         <v>11528550</v>
       </c>
-      <c r="D28">
-        <v>0</v>
-      </c>
       <c r="E28">
         <v>0</v>
       </c>
@@ -2240,11 +2276,11 @@
         <v>0</v>
       </c>
       <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
         <v>27.42</v>
       </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
       <c r="P28">
         <v>0</v>
       </c>
@@ -2254,27 +2290,23 @@
       <c r="R28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Saman</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>0</v>
+      <c r="S28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
+      <c r="A29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
       </c>
       <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
         <v>-437.5</v>
       </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
       <c r="F29">
         <v>0</v>
       </c>
@@ -2300,11 +2332,11 @@
         <v>0</v>
       </c>
       <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29">
         <v>11.23</v>
       </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
       <c r="P29">
         <v>0</v>
       </c>
@@ -2314,56 +2346,52 @@
       <c r="R29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>İşletme sermayesi</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C30">
+      <c r="S29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
+      <c r="A30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30">
         <v>758079000</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>239.38</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>280.73</v>
       </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
         <v>469.2</v>
       </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
       <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
         <v>901.47</v>
       </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
       <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
         <v>1899.15</v>
       </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
       <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30">
         <v>3491.9</v>
-      </c>
-      <c r="O30">
-        <v>12.5</v>
       </c>
       <c r="P30">
         <v>12.5</v>
@@ -2372,26 +2400,22 @@
         <v>12.5</v>
       </c>
       <c r="R30">
+        <v>12.5</v>
+      </c>
+      <c r="S30">
         <v>-1</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Ahır Yeri</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C31">
+    <row r="31" spans="1:19">
+      <c r="A31" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31">
         <v>300000</v>
       </c>
-      <c r="D31">
-        <v>0</v>
-      </c>
       <c r="E31">
         <v>0</v>
       </c>
@@ -2420,11 +2444,11 @@
         <v>0</v>
       </c>
       <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31">
         <v>6</v>
       </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
       <c r="P31">
         <v>0</v>
       </c>
@@ -2432,6 +2456,9 @@
         <v>0</v>
       </c>
       <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
         <v>0</v>
       </c>
     </row>
@@ -2449,38 +2476,28 @@
     <col min="2" max="2" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>54</v>
       </c>
       <c r="B1">
         <v>799198102.8839999</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>OPTIMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Solution is optimal</t>
-        </is>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2502,48 +2519,32 @@
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>reduced_cost</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>original_value</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>lower_bound</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>upper_bound</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>is_basic_variable</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Buğday</t>
-        </is>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
       <c r="B2">
         <v>870.388</v>
@@ -2564,11 +2565,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Buğday+SM</t>
-        </is>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <v>57380</v>
@@ -2589,11 +2588,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Buğday satış</t>
-        </is>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>5</v>
       </c>
       <c r="B4">
         <v>25484544.825</v>
@@ -2614,11 +2611,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Silajlık mısır satış</t>
-        </is>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2639,11 +2634,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Çeltik</t>
-        </is>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>7</v>
       </c>
       <c r="B6">
         <v>30019.612</v>
@@ -2664,11 +2657,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Çeltik satış</t>
-        </is>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>8</v>
       </c>
       <c r="B7">
         <v>21013728.281</v>
@@ -2689,11 +2680,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Fındık</t>
-        </is>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>9</v>
       </c>
       <c r="B8">
         <v>20531</v>
@@ -2714,11 +2703,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Fındık satış</t>
-        </is>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>10</v>
       </c>
       <c r="B9">
         <v>1924781.25</v>
@@ -2739,11 +2726,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Buğday+lahana</t>
-        </is>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>11</v>
       </c>
       <c r="B10">
         <v>30525</v>
@@ -2764,11 +2749,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Lahana satış</t>
-        </is>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>12</v>
       </c>
       <c r="B11">
         <v>183150000</v>
@@ -2789,11 +2772,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Süt sığırcılığı</t>
-        </is>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>13</v>
       </c>
       <c r="B12">
         <v>33908.711</v>
@@ -2814,11 +2795,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>igk6</t>
-        </is>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>14</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2839,11 +2818,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>igk7</t>
-        </is>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>15</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2864,11 +2841,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>igk8</t>
-        </is>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>16</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2889,11 +2864,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sermaye temini</t>
-        </is>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>17</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2933,48 +2906,32 @@
     <col min="7" max="7" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>constraint</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>shadow_price</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>slack_or_surplus</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>original_value</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>lower_bound</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>upper_bound</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>neither_bounds_are_binding</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Toplam arazi</t>
-        </is>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>23</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2995,11 +2952,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Toplam kuru tarla arazisi</t>
-        </is>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>25</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -3020,11 +2975,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Toplam sulu tarla arazisi</t>
-        </is>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>26</v>
       </c>
       <c r="B4">
         <v>1280.8</v>
@@ -3045,11 +2998,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Meyve arazisi</t>
-        </is>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>27</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3070,11 +3021,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sebze arazisi</t>
-        </is>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>28</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3095,11 +3044,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Buğday arazisi</t>
-        </is>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>29</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3120,11 +3067,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Silajlık mısır arazisi</t>
-        </is>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>30</v>
       </c>
       <c r="B8">
         <v>2868.086</v>
@@ -3145,11 +3090,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Çeltik arazisi</t>
-        </is>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>31</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3170,11 +3113,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fındık arazisi</t>
-        </is>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>32</v>
       </c>
       <c r="B10">
         <v>1465.717</v>
@@ -3195,11 +3136,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Lahana arazisi</t>
-        </is>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>33</v>
       </c>
       <c r="B11">
         <v>16100.85</v>
@@ -3220,11 +3159,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Buğday transfer</t>
-        </is>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>34</v>
       </c>
       <c r="B12">
         <v>2.3</v>
@@ -3245,11 +3182,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Silajlık mısır transfer</t>
-        </is>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>35</v>
       </c>
       <c r="B13">
         <v>4.138</v>
@@ -3270,11 +3205,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Çeltik transfer</t>
-        </is>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>36</v>
       </c>
       <c r="B14">
         <v>2.5</v>
@@ -3295,11 +3228,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Lahana transfer</t>
-        </is>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>37</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -3320,11 +3251,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fındık transfer</t>
-        </is>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>38</v>
       </c>
       <c r="B16">
         <v>25.25</v>
@@ -3345,11 +3274,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>İşgücü Ocak</t>
-        </is>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>39</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3370,11 +3297,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>İşgücü Şubat</t>
-        </is>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>40</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3395,11 +3320,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>İşgücü Mart</t>
-        </is>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>41</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3420,11 +3343,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>İşgücü Nisan</t>
-        </is>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>42</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3445,11 +3366,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>İşgücü Mayıs</t>
-        </is>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>43</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3470,11 +3389,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>İşgücü Haziran</t>
-        </is>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>44</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3495,11 +3412,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>İşgücü Temmuz</t>
-        </is>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>45</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3520,11 +3435,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>İşgücü Ağustos</t>
-        </is>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>46</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3545,11 +3458,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>İşgücü Eylül</t>
-        </is>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>47</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3570,11 +3481,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>İşgücü Ekim</t>
-        </is>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>48</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3595,11 +3504,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>İşgücü Kasım</t>
-        </is>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>49</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3620,11 +3527,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>İşgücü Aralık</t>
-        </is>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>50</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3645,11 +3550,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Saman</t>
-        </is>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>51</v>
       </c>
       <c r="B29">
         <v>1.175</v>
@@ -3670,11 +3573,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>İşletme sermayesi</t>
-        </is>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>52</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3695,11 +3596,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Ahır Yeri</t>
-        </is>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>53</v>
       </c>
       <c r="B31">
         <v>0</v>

--- a/test/integration/01-out.xlsx
+++ b/test/integration/01-out.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="66">
   <si>
     <t>variable</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>constraint</t>
-  </si>
-  <si>
-    <t>id</t>
   </si>
   <si>
     <t>relation</t>
@@ -699,31 +696,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.85546875" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="3.5703125" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" customWidth="1"/>
-    <col min="11" max="11" width="6.140625" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="7" width="18.5703125" customWidth="1"/>
+    <col min="8" max="8" width="6.140625" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
+    <col min="10" max="10" width="6.140625" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" customWidth="1"/>
+    <col min="15" max="15" width="4.42578125" customWidth="1"/>
     <col min="16" max="16" width="4.42578125" customWidth="1"/>
     <col min="17" max="17" width="4.42578125" customWidth="1"/>
-    <col min="18" max="18" width="4.42578125" customWidth="1"/>
-    <col min="19" max="19" width="13.28515625" customWidth="1"/>
+    <col min="18" max="18" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -734,632 +730,632 @@
         <v>21</v>
       </c>
       <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2">
+        <v>602620</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="D2">
-        <v>602620</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>359641</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3">
-        <v>359641</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4">
+        <v>88270</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4">
-        <v>88270</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
+        <v>25396</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5">
-        <v>25396</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>74740</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6">
-        <v>74740</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>253452</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" t="s">
         <v>29</v>
       </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7">
-        <v>253452</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>57380</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" t="s">
         <v>30</v>
       </c>
-      <c r="C8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8">
-        <v>57380</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9">
+        <v>334876</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" t="s">
         <v>31</v>
       </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9">
-        <v>334876</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10">
+        <v>20531</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10">
-        <v>20531</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>1</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11">
+        <v>30525</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" t="s">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11">
-        <v>30525</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19">
-      <c r="A12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>-437.5</v>
       </c>
       <c r="E12">
         <v>-437.5</v>
       </c>
       <c r="F12">
-        <v>-437.5</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1394,724 +1390,724 @@
       <c r="R12">
         <v>0</v>
       </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19">
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>-827.33</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>1400</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" t="s">
         <v>35</v>
       </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>-827.33</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>1400</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>-700</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" t="s">
         <v>36</v>
       </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>-700</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>-6000</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" t="s">
         <v>37</v>
       </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>-6000</v>
-      </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>-93.75</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" t="s">
         <v>38</v>
       </c>
-      <c r="C16" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>-93.75</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17">
+        <v>11528550</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>27.42</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" t="s">
         <v>39</v>
       </c>
-      <c r="C17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17">
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
         <v>11528550</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>0</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>25.55</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>11528550</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
         <v>27.42</v>
       </c>
-      <c r="P17">
-        <v>0</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19">
-      <c r="A18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18">
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20">
         <v>11528550</v>
       </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>25.55</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19">
-      <c r="A19" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19">
-        <v>11528550</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>27.42</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19">
-      <c r="A20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C20" t="s">
-        <v>24</v>
-      </c>
       <c r="D20">
-        <v>11528550</v>
+        <v>0.88</v>
       </c>
       <c r="E20">
         <v>0.88</v>
       </c>
       <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>1.76</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2.5</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>1.76</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>27.32</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21">
+        <v>11528550</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
         <v>0.88</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>1.76</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>2.5</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>1.76</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>27.32</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20">
-        <v>0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19">
-      <c r="A21" t="s">
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>27.42</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" t="s">
         <v>43</v>
       </c>
-      <c r="C21" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21">
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22">
         <v>11528550</v>
       </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0.88</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0</v>
-      </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>27.42</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21">
-        <v>0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19">
-      <c r="A22" t="s">
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>1.08</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>27.37</v>
+      </c>
+      <c r="O22">
+        <v>-1</v>
+      </c>
+      <c r="P22">
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" t="s">
         <v>44</v>
       </c>
-      <c r="C22" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22">
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23">
         <v>11528550</v>
       </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>1.08</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>27.37</v>
-      </c>
-      <c r="P22">
-        <v>-1</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19">
-      <c r="A23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" t="s">
-        <v>24</v>
-      </c>
       <c r="D23">
-        <v>11528550</v>
+        <v>3.17</v>
       </c>
       <c r="E23">
         <v>3.17</v>
       </c>
       <c r="F23">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="I23">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="K23">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>6.34</v>
       </c>
       <c r="M23">
-        <v>6.34</v>
+        <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>27.42</v>
       </c>
       <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>-1</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24">
+        <v>11528550</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>12.5</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
         <v>27.42</v>
       </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
         <v>-1</v>
       </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19">
-      <c r="A24" t="s">
+      <c r="R24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" t="s">
         <v>46</v>
       </c>
-      <c r="C24" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24">
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25">
         <v>11528550</v>
       </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24">
-        <v>0</v>
-      </c>
-      <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24">
-        <v>12.5</v>
-      </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
-        <v>27.42</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <v>0</v>
-      </c>
-      <c r="R24">
-        <v>-1</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19">
-      <c r="A25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" t="s">
-        <v>24</v>
-      </c>
       <c r="D25">
-        <v>11528550</v>
+        <v>0.73</v>
       </c>
       <c r="E25">
         <v>0.73</v>
       </c>
       <c r="F25">
-        <v>0.73</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="I25">
-        <v>10.25</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="K25">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M25">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>27.37</v>
       </c>
       <c r="O25">
-        <v>27.37</v>
+        <v>0</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -2122,34 +2118,34 @@
       <c r="R25">
         <v>0</v>
       </c>
-      <c r="S25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19">
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" t="s">
-        <v>24</v>
+        <v>47</v>
+      </c>
+      <c r="B26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26">
+        <v>11528550</v>
       </c>
       <c r="D26">
-        <v>11528550</v>
+        <v>0.88</v>
       </c>
       <c r="E26">
         <v>0.88</v>
       </c>
       <c r="F26">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I26">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -2158,240 +2154,240 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M26">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>27.42</v>
       </c>
       <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27">
+        <v>11528550</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>27.32</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28">
+        <v>11528550</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
         <v>27.42</v>
       </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19">
-      <c r="A27" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27">
-        <v>11528550</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>0</v>
-      </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>27.32</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <v>0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19">
-      <c r="A28" t="s">
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" t="s">
         <v>50</v>
       </c>
-      <c r="C28" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28">
-        <v>11528550</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>27.42</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19">
-      <c r="A29" t="s">
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>-437.5</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>11.23</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" t="s">
         <v>51</v>
       </c>
-      <c r="C29" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>-437.5</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>11.23</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19">
-      <c r="A30" t="s">
-        <v>52</v>
-      </c>
-      <c r="C30" t="s">
-        <v>24</v>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30">
+        <v>758079000</v>
       </c>
       <c r="D30">
-        <v>758079000</v>
+        <v>239.38</v>
       </c>
       <c r="E30">
-        <v>239.38</v>
+        <v>280.73</v>
       </c>
       <c r="F30">
-        <v>280.73</v>
+        <v>0</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>469.2</v>
       </c>
       <c r="I30">
-        <v>469.2</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>901.47</v>
       </c>
       <c r="K30">
-        <v>901.47</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1899.15</v>
       </c>
       <c r="M30">
-        <v>1899.15</v>
+        <v>0</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>3491.9</v>
       </c>
       <c r="O30">
-        <v>3491.9</v>
+        <v>12.5</v>
       </c>
       <c r="P30">
         <v>12.5</v>
@@ -2400,21 +2396,21 @@
         <v>12.5</v>
       </c>
       <c r="R30">
-        <v>12.5</v>
-      </c>
-      <c r="S30">
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" t="s">
-        <v>24</v>
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31">
+        <v>300000</v>
       </c>
       <c r="D31">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2444,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O31">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -2456,9 +2452,6 @@
         <v>0</v>
       </c>
       <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
         <v>0</v>
       </c>
     </row>
@@ -2478,7 +2471,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1">
         <v>799198102.8839999</v>
@@ -2486,18 +2479,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" t="s">
         <v>55</v>
-      </c>
-      <c r="B2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" t="s">
         <v>57</v>
-      </c>
-      <c r="B3" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2524,22 +2517,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>62</v>
-      </c>
-      <c r="G1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -2911,27 +2904,27 @@
         <v>19</v>
       </c>
       <c r="B1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" t="s">
         <v>64</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s">
         <v>65</v>
-      </c>
-      <c r="D1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2954,7 +2947,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2977,7 +2970,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>1280.8</v>
@@ -3000,7 +2993,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3023,7 +3016,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3046,7 +3039,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3069,7 +3062,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8">
         <v>2868.086</v>
@@ -3092,7 +3085,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3115,7 +3108,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10">
         <v>1465.717</v>
@@ -3138,7 +3131,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>16100.85</v>
@@ -3161,7 +3154,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12">
         <v>2.3</v>
@@ -3184,7 +3177,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>4.138</v>
@@ -3207,7 +3200,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14">
         <v>2.5</v>
@@ -3230,7 +3223,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -3253,7 +3246,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16">
         <v>25.25</v>
@@ -3276,7 +3269,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3299,7 +3292,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3322,7 +3315,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3345,7 +3338,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3368,7 +3361,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3391,7 +3384,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3414,7 +3407,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3437,7 +3430,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3460,7 +3453,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3483,7 +3476,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3506,7 +3499,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3529,7 +3522,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3552,7 +3545,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29">
         <v>1.175</v>
@@ -3575,7 +3568,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3598,7 +3591,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B31">
         <v>0</v>

--- a/test/integration/01-out.xlsx
+++ b/test/integration/01-out.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="66">
   <si>
     <t>variable</t>
   </si>
@@ -29,6 +29,9 @@
     <t>name</t>
   </si>
   <si>
+    <t>method</t>
+  </si>
+  <si>
     <t>Buğday</t>
   </si>
   <si>
@@ -74,9 +77,6 @@
     <t>Sermaye temini</t>
   </si>
   <si>
-    <t>{}</t>
-  </si>
-  <si>
     <t>constraint</t>
   </si>
   <si>
@@ -86,12 +86,51 @@
     <t>rhs</t>
   </si>
   <si>
+    <t>&lt;=</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>OPTIMAL</t>
+  </si>
+  <si>
+    <t>Solution is optimal</t>
+  </si>
+  <si>
+    <t>reduced_cost</t>
+  </si>
+  <si>
+    <t>original_value</t>
+  </si>
+  <si>
+    <t>lower_bound</t>
+  </si>
+  <si>
+    <t>upper_bound</t>
+  </si>
+  <si>
+    <t>is_basic_variable</t>
+  </si>
+  <si>
+    <t>shadow_price</t>
+  </si>
+  <si>
+    <t>slack_or_surplus</t>
+  </si>
+  <si>
+    <t>neither_bounds_are_binding</t>
+  </si>
+  <si>
     <t>Toplam arazi</t>
   </si>
   <si>
-    <t>&lt;=</t>
-  </si>
-  <si>
     <t>Toplam kuru tarla arazisi</t>
   </si>
   <si>
@@ -177,45 +216,6 @@
   </si>
   <si>
     <t>Ahır Yeri</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>OPTIMAL</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>Solution is optimal</t>
-  </si>
-  <si>
-    <t>reduced_cost</t>
-  </si>
-  <si>
-    <t>original_value</t>
-  </si>
-  <si>
-    <t>lower_bound</t>
-  </si>
-  <si>
-    <t>upper_bound</t>
-  </si>
-  <si>
-    <t>is_basic_variable</t>
-  </si>
-  <si>
-    <t>shadow_price</t>
-  </si>
-  <si>
-    <t>slack_or_surplus</t>
-  </si>
-  <si>
-    <t>neither_bounds_are_binding</t>
   </si>
 </sst>
 </file>
@@ -547,15 +547,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" customWidth="1"/>
     <col min="3" max="3" width="4.42578125" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -565,125 +566,125 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>-239.38</v>
       </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>-280.73</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>2.3</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>1.33</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>-469.2</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>-901.47</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>25.25</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>-1899.15</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>5806.18</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>-12.5</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>-12.5</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>-12.5</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>-0.25</v>
@@ -699,7 +700,7 @@
   <dimension ref="A1:R31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="3.5703125" customWidth="1"/>
     <col min="4" max="4" width="6.140625" customWidth="1"/>
@@ -730,57 +731,54 @@
         <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
       </c>
       <c r="C2">
         <v>602620</v>
@@ -832,11 +830,8 @@
       </c>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>359641</v>
@@ -888,11 +883,8 @@
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4">
         <v>88270</v>
@@ -944,11 +936,8 @@
       </c>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5">
         <v>25396</v>
@@ -1000,11 +989,8 @@
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>74740</v>
@@ -1056,11 +1042,8 @@
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7">
         <v>253452</v>
@@ -1112,11 +1095,8 @@
       </c>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" t="s">
-        <v>29</v>
-      </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8">
         <v>57380</v>
@@ -1168,11 +1148,8 @@
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" t="s">
-        <v>30</v>
-      </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9">
         <v>334876</v>
@@ -1224,11 +1201,8 @@
       </c>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10">
         <v>20531</v>
@@ -1280,11 +1254,8 @@
       </c>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" t="s">
-        <v>32</v>
-      </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11">
         <v>30525</v>
@@ -1336,11 +1307,8 @@
       </c>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" t="s">
-        <v>33</v>
-      </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1392,11 +1360,8 @@
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" t="s">
-        <v>34</v>
-      </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1448,11 +1413,8 @@
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1504,11 +1466,8 @@
       </c>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" t="s">
-        <v>36</v>
-      </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1560,11 +1519,8 @@
       </c>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" t="s">
-        <v>37</v>
-      </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1615,12 +1571,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
-      <c r="A17" t="s">
-        <v>38</v>
-      </c>
+    <row r="17" spans="2:18">
       <c r="B17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17">
         <v>11528550</v>
@@ -1671,12 +1624,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
-      <c r="A18" t="s">
-        <v>39</v>
-      </c>
+    <row r="18" spans="2:18">
       <c r="B18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18">
         <v>11528550</v>
@@ -1727,12 +1677,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
-      <c r="A19" t="s">
-        <v>40</v>
-      </c>
+    <row r="19" spans="2:18">
       <c r="B19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19">
         <v>11528550</v>
@@ -1783,12 +1730,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
+    <row r="20" spans="2:18">
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>11528550</v>
@@ -1839,12 +1783,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
-      <c r="A21" t="s">
-        <v>42</v>
-      </c>
+    <row r="21" spans="2:18">
       <c r="B21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21">
         <v>11528550</v>
@@ -1895,12 +1836,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
-      <c r="A22" t="s">
-        <v>43</v>
-      </c>
+    <row r="22" spans="2:18">
       <c r="B22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22">
         <v>11528550</v>
@@ -1951,12 +1889,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
+    <row r="23" spans="2:18">
       <c r="B23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23">
         <v>11528550</v>
@@ -2007,12 +1942,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
-      <c r="A24" t="s">
-        <v>45</v>
-      </c>
+    <row r="24" spans="2:18">
       <c r="B24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C24">
         <v>11528550</v>
@@ -2063,12 +1995,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
-      <c r="A25" t="s">
-        <v>46</v>
-      </c>
+    <row r="25" spans="2:18">
       <c r="B25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C25">
         <v>11528550</v>
@@ -2119,12 +2048,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
-      <c r="A26" t="s">
-        <v>47</v>
-      </c>
+    <row r="26" spans="2:18">
       <c r="B26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26">
         <v>11528550</v>
@@ -2175,12 +2101,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
-      <c r="A27" t="s">
-        <v>48</v>
-      </c>
+    <row r="27" spans="2:18">
       <c r="B27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C27">
         <v>11528550</v>
@@ -2231,12 +2154,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
-      <c r="A28" t="s">
-        <v>49</v>
-      </c>
+    <row r="28" spans="2:18">
       <c r="B28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C28">
         <v>11528550</v>
@@ -2287,12 +2207,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
-      <c r="A29" t="s">
-        <v>50</v>
-      </c>
+    <row r="29" spans="2:18">
       <c r="B29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -2343,12 +2260,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
-      <c r="A30" t="s">
-        <v>51</v>
-      </c>
+    <row r="30" spans="2:18">
       <c r="B30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C30">
         <v>758079000</v>
@@ -2399,12 +2313,9 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
-      <c r="A31" t="s">
-        <v>52</v>
-      </c>
+    <row r="31" spans="2:18">
       <c r="B31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C31">
         <v>300000</v>
@@ -2462,35 +2373,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B1">
+        <v>23</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2">
         <v>799198102.8839999</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2517,27 +2427,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C1" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G1" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>870.388</v>
@@ -2560,7 +2470,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>57380</v>
@@ -2583,7 +2493,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>25484544.825</v>
@@ -2606,7 +2516,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -2629,7 +2539,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>30019.612</v>
@@ -2652,7 +2562,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>21013728.281</v>
@@ -2675,7 +2585,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>20531</v>
@@ -2698,7 +2608,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>1924781.25</v>
@@ -2721,7 +2631,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>30525</v>
@@ -2744,7 +2654,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>183150000</v>
@@ -2767,7 +2677,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>33908.711</v>
@@ -2790,7 +2700,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -2813,7 +2723,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2836,7 +2746,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -2859,7 +2769,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2904,27 +2814,27 @@
         <v>19</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="E1" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="F1" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="G1" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -2947,7 +2857,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -2970,7 +2880,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B4">
         <v>1280.8</v>
@@ -2993,7 +2903,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -3016,7 +2926,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -3039,7 +2949,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -3062,7 +2972,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B8">
         <v>2868.086</v>
@@ -3085,7 +2995,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -3108,7 +3018,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B10">
         <v>1465.717</v>
@@ -3131,7 +3041,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B11">
         <v>16100.85</v>
@@ -3154,7 +3064,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="B12">
         <v>2.3</v>
@@ -3177,7 +3087,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B13">
         <v>4.138</v>
@@ -3200,7 +3110,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B14">
         <v>2.5</v>
@@ -3223,7 +3133,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -3246,7 +3156,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B16">
         <v>25.25</v>
@@ -3269,7 +3179,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -3292,7 +3202,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -3315,7 +3225,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -3338,7 +3248,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -3361,7 +3271,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -3384,7 +3294,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -3407,7 +3317,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -3430,7 +3340,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -3453,7 +3363,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -3476,7 +3386,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -3499,7 +3409,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -3522,7 +3432,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -3545,7 +3455,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="B29">
         <v>1.175</v>
@@ -3568,7 +3478,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -3591,7 +3501,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B31">
         <v>0</v>
